--- a/ML-Current/polystyrene-imputated-solvents-hot-encoded-2-23-25.xlsx
+++ b/ML-Current/polystyrene-imputated-solvents-hot-encoded-2-23-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dillo\OneDrive\Documents\GitHub\LCCC-ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aced77f8e52479c3/Documents/GitHub/Dr.Wang_pr/ML-Current/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F153BD78-7ACE-4C5C-AF38-B1124B8450D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="428" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -971,153 +971,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:GL173"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.86328125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="31.73046875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.1328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.265625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="21" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="25.59765625" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="28" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.265625" bestFit="1" customWidth="1"/>
     <col min="38" max="49" width="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="58" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="58" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="16.3984375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="17" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="21.265625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="8.1328125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="12" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="22.86328125" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="20" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="86" max="94" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="95" max="97" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="99" max="105" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="24.1328125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="29.265625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="86" max="94" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="95" max="97" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="99" max="105" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="16.1328125" bestFit="1" customWidth="1"/>
     <col min="107" max="113" width="16" bestFit="1" customWidth="1"/>
     <col min="114" max="114" width="17" bestFit="1" customWidth="1"/>
     <col min="115" max="115" width="10" bestFit="1" customWidth="1"/>
-    <col min="116" max="124" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="116" max="124" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="128" max="128" width="19" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="15.73046875" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="24.59765625" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="19.86328125" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="29.73046875" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="24.73046875" bestFit="1" customWidth="1"/>
     <col min="156" max="156" width="38" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="36.73046875" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="32.73046875" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="33.86328125" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="31.59765625" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="33.1328125" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="33.265625" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="31.59765625" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="29.86328125" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="38.59765625" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="33.1328125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="33.73046875" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="36.73046875" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="32.1328125" bestFit="1" customWidth="1"/>
     <col min="174" max="174" width="37" bestFit="1" customWidth="1"/>
-    <col min="175" max="175" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="184" max="184" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="46.73046875" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="33.3984375" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="23.1328125" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="30.73046875" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="32.3984375" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="34.59765625" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="47.86328125" bestFit="1" customWidth="1"/>
+    <col min="184" max="184" width="39.86328125" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="32.1328125" bestFit="1" customWidth="1"/>
     <col min="187" max="187" width="36" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="32.86328125" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="25.73046875" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="23.59765625" bestFit="1" customWidth="1"/>
     <col min="191" max="191" width="35" bestFit="1" customWidth="1"/>
     <col min="192" max="192" width="47" bestFit="1" customWidth="1"/>
     <col min="193" max="193" width="40" bestFit="1" customWidth="1"/>
-    <col min="194" max="194" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="194" max="194" width="19.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>53</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>50</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>56.6</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>0</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>0</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>0</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>0</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>0</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>0</v>
       </c>
@@ -7541,7 +7541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>39</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>52</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>0</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>0</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>0</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>0</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>43.6</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>55.8</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>25.7</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>36.5</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>0</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>0</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>0</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>0</v>
       </c>
@@ -15717,7 +15717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>0</v>
       </c>
@@ -16301,7 +16301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>62</v>
       </c>
@@ -16885,7 +16885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>50</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>18.3</v>
       </c>
@@ -18053,7 +18053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>55.8</v>
       </c>
@@ -18637,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>0</v>
       </c>
@@ -19221,7 +19221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>0</v>
       </c>
@@ -19805,7 +19805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>0</v>
       </c>
@@ -20389,7 +20389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>0</v>
       </c>
@@ -20973,7 +20973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>0</v>
       </c>
@@ -21557,7 +21557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>0</v>
       </c>
@@ -22141,7 +22141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>0</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>0</v>
       </c>
@@ -23309,7 +23309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>0</v>
       </c>
@@ -23893,7 +23893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>0</v>
       </c>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>52.1</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>0</v>
       </c>
@@ -25645,7 +25645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>52.1</v>
       </c>
@@ -26229,7 +26229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>0</v>
       </c>
@@ -26813,7 +26813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>0</v>
       </c>
@@ -27397,7 +27397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>0</v>
       </c>
@@ -27981,7 +27981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>0</v>
       </c>
@@ -28565,7 +28565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>0</v>
       </c>
@@ -29149,7 +29149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>0</v>
       </c>
@@ -29733,7 +29733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>0</v>
       </c>
@@ -30317,7 +30317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>65.400000000000006</v>
       </c>
@@ -30901,7 +30901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>55</v>
       </c>
@@ -31485,7 +31485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>55</v>
       </c>
@@ -32069,7 +32069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>50</v>
       </c>
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>51</v>
       </c>
@@ -33237,7 +33237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>52</v>
       </c>
@@ -33821,7 +33821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>53</v>
       </c>
@@ -34405,7 +34405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>54</v>
       </c>
@@ -34989,7 +34989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>55</v>
       </c>
@@ -35573,7 +35573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>60.3</v>
       </c>
@@ -36157,7 +36157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>49.6</v>
       </c>
@@ -36741,7 +36741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>31</v>
       </c>
@@ -37325,7 +37325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>49.7</v>
       </c>
@@ -37909,7 +37909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>62.9</v>
       </c>
@@ -38493,7 +38493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>62.3</v>
       </c>
@@ -39077,7 +39077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>16.100000000000001</v>
       </c>
@@ -39661,7 +39661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>22.7</v>
       </c>
@@ -40245,7 +40245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>56.6</v>
       </c>
@@ -40829,7 +40829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>0</v>
       </c>
@@ -41413,7 +41413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>0</v>
       </c>
@@ -41997,7 +41997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>0</v>
       </c>
@@ -42581,7 +42581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>0</v>
       </c>
@@ -43165,7 +43165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>51.8</v>
       </c>
@@ -43749,7 +43749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>48.7</v>
       </c>
@@ -44333,7 +44333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>0</v>
       </c>
@@ -44917,7 +44917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>0</v>
       </c>
@@ -45501,7 +45501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>0</v>
       </c>
@@ -46085,7 +46085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>0</v>
       </c>
@@ -46669,7 +46669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>0</v>
       </c>
@@ -47253,7 +47253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>52.1</v>
       </c>
@@ -47837,7 +47837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>0</v>
       </c>
@@ -48421,7 +48421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>0</v>
       </c>
@@ -49005,7 +49005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>53</v>
       </c>
@@ -49589,7 +49589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>47.4</v>
       </c>
@@ -50173,7 +50173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>20.100000000000001</v>
       </c>
@@ -50757,7 +50757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>16.100000000000001</v>
       </c>
@@ -51341,7 +51341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>55.8</v>
       </c>
@@ -51925,7 +51925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>62.9</v>
       </c>
@@ -52509,7 +52509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>31</v>
       </c>
@@ -53093,7 +53093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>62.3</v>
       </c>
@@ -53677,7 +53677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>0</v>
       </c>
@@ -54261,7 +54261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>0</v>
       </c>
@@ -54845,7 +54845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>0</v>
       </c>
@@ -55429,7 +55429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>0</v>
       </c>
@@ -56013,7 +56013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>0</v>
       </c>
@@ -56597,7 +56597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>0</v>
       </c>
@@ -57181,7 +57181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>47.6</v>
       </c>
@@ -57765,7 +57765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>47.6</v>
       </c>
@@ -58349,7 +58349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>57</v>
       </c>
@@ -58933,7 +58933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>41.9</v>
       </c>
@@ -59517,7 +59517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>0</v>
       </c>
@@ -60101,7 +60101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>0</v>
       </c>
@@ -60685,7 +60685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>55</v>
       </c>
@@ -61269,7 +61269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>0</v>
       </c>
@@ -61853,7 +61853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>0</v>
       </c>
@@ -62437,7 +62437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>0</v>
       </c>
@@ -63021,7 +63021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>0</v>
       </c>
@@ -63605,7 +63605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>0</v>
       </c>
@@ -64189,7 +64189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>0</v>
       </c>
@@ -64773,7 +64773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>0</v>
       </c>
@@ -65357,7 +65357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>0</v>
       </c>
@@ -65941,7 +65941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>0</v>
       </c>
@@ -66525,7 +66525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>0</v>
       </c>
@@ -67109,7 +67109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>51</v>
       </c>
@@ -67693,7 +67693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>0</v>
       </c>
@@ -68277,7 +68277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>59</v>
       </c>
@@ -68861,7 +68861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>59</v>
       </c>
@@ -69445,7 +69445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>55</v>
       </c>
@@ -70029,7 +70029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>55</v>
       </c>
@@ -70613,7 +70613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>55</v>
       </c>
@@ -71197,7 +71197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>0</v>
       </c>
@@ -71781,7 +71781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>55</v>
       </c>
@@ -72365,7 +72365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>42</v>
       </c>
@@ -72949,7 +72949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>0</v>
       </c>
@@ -73533,7 +73533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>0</v>
       </c>
@@ -74117,7 +74117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>0</v>
       </c>
@@ -74701,7 +74701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>0</v>
       </c>
@@ -75285,7 +75285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>0</v>
       </c>
@@ -75869,7 +75869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>0</v>
       </c>
@@ -76453,7 +76453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>0</v>
       </c>
@@ -77037,7 +77037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>0</v>
       </c>
@@ -77621,7 +77621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>0</v>
       </c>
@@ -78205,7 +78205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>0</v>
       </c>
@@ -78789,7 +78789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>0</v>
       </c>
@@ -79373,7 +79373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>0</v>
       </c>
@@ -79957,7 +79957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>0</v>
       </c>
@@ -80541,7 +80541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>0</v>
       </c>
@@ -81125,7 +81125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>0</v>
       </c>
@@ -81709,7 +81709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>58</v>
       </c>
@@ -82293,7 +82293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>0</v>
       </c>
@@ -82877,7 +82877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>0</v>
       </c>
@@ -83461,7 +83461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>0</v>
       </c>
@@ -84045,7 +84045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>0</v>
       </c>
@@ -84629,7 +84629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>57</v>
       </c>
@@ -85213,7 +85213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>57</v>
       </c>
@@ -85797,7 +85797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>57</v>
       </c>
@@ -86381,7 +86381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>0</v>
       </c>
@@ -86965,7 +86965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>0</v>
       </c>
@@ -87549,7 +87549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>0</v>
       </c>
@@ -88133,7 +88133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>0</v>
       </c>
@@ -88717,7 +88717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>0</v>
       </c>
@@ -89301,7 +89301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>0</v>
       </c>
@@ -89885,7 +89885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>0</v>
       </c>
@@ -90469,7 +90469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>58</v>
       </c>
@@ -91053,7 +91053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>0</v>
       </c>
@@ -91637,7 +91637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>0</v>
       </c>
@@ -92221,7 +92221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>53</v>
       </c>
@@ -92805,7 +92805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>62.15</v>
       </c>
@@ -93389,7 +93389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>52.1</v>
       </c>
@@ -93973,7 +93973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>55</v>
       </c>
@@ -94557,7 +94557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>55.8</v>
       </c>
@@ -95141,7 +95141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>31</v>
       </c>
@@ -95725,7 +95725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>62.9</v>
       </c>
@@ -96309,7 +96309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>16.100000000000001</v>
       </c>
@@ -96893,7 +96893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>0</v>
       </c>
@@ -97477,7 +97477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>0</v>
       </c>
@@ -98061,7 +98061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>47.6</v>
       </c>
@@ -98645,7 +98645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>55</v>
       </c>
@@ -99229,7 +99229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>0</v>
       </c>
@@ -99813,7 +99813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>51.5</v>
       </c>
@@ -100397,7 +100397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>0</v>
       </c>
@@ -100981,7 +100981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>57</v>
       </c>
@@ -101565,7 +101565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:194" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:194" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>0</v>
       </c>
